--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportConfirmManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportConfirmManage001.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E5168D-536D-4EA3-939A-406B72F59CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18530" windowHeight="7130"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="报表确认" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>确认状态</t>
   </si>
@@ -52,12 +58,6 @@
     <t>确认时间</t>
   </si>
   <si>
-    <t>确认复核人</t>
-  </si>
-  <si>
-    <t>复核时间</t>
-  </si>
-  <si>
     <t>上传说明</t>
   </si>
   <si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>确认方式</t>
-  </si>
-  <si>
-    <t>披露渠道</t>
   </si>
   <si>
     <t>披露方式</t>
@@ -79,15 +76,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,151 +97,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,198 +125,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -477,252 +153,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -742,62 +176,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="常规 10" xfId="47"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
+    <cellStyle name="常规 10" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1084,36 +474,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:T32"/>
-  <sheetFormatPr defaultColWidth="13.6272727272727" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q32"/>
+  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.1272727272727" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.1272727272727" style="3" customWidth="1"/>
-    <col min="3" max="3" width="24.3727272727273" style="3" customWidth="1"/>
-    <col min="4" max="6" width="36.2545454545455" style="4" customWidth="1"/>
-    <col min="7" max="7" width="24.8727272727273" style="4" customWidth="1"/>
-    <col min="8" max="8" width="41.7545454545455" style="4" customWidth="1"/>
-    <col min="9" max="9" width="43.2545454545455" style="5" customWidth="1"/>
-    <col min="10" max="11" width="20.5" style="5" customWidth="1"/>
-    <col min="12" max="14" width="16.2545454545455" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.8727272727273" style="3" customWidth="1"/>
-    <col min="16" max="16" width="16.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="13.6272727272727" style="3"/>
-    <col min="18" max="18" width="20.5" style="3" customWidth="1"/>
-    <col min="19" max="19" width="11.7545454545455" style="3" customWidth="1"/>
-    <col min="20" max="20" width="40.7545454545455" style="3" customWidth="1"/>
-    <col min="21" max="21" width="14.2545454545455" customWidth="1"/>
-    <col min="25" max="25" width="14.7545454545455" customWidth="1"/>
-    <col min="26" max="26" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="3" customWidth="1"/>
+    <col min="4" max="6" width="36.21875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.77734375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="43.21875" style="5" customWidth="1"/>
+    <col min="10" max="11" width="20.44140625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="16.21875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.88671875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="3"/>
+    <col min="16" max="16" width="11.77734375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="40.77734375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" customWidth="1"/>
+    <col min="22" max="22" width="14.77734375" customWidth="1"/>
+    <col min="23" max="23" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:20">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1165,17 +554,8 @@
       <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1193,11 +573,8 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1215,11 +592,8 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="4" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1237,11 +611,8 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="5" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1259,11 +630,8 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1281,11 +649,8 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="7" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1303,11 +668,8 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1325,11 +687,8 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="9" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1347,11 +706,8 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="10" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1369,11 +725,8 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1391,11 +744,8 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1413,11 +763,8 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -1435,11 +782,8 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1457,11 +801,8 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1479,11 +820,8 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1501,11 +839,8 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="17" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1523,11 +858,8 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="18" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1545,11 +877,8 @@
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="19" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1567,11 +896,8 @@
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1589,11 +915,8 @@
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="21" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1611,11 +934,8 @@
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1633,11 +953,8 @@
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="23" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1655,11 +972,8 @@
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="24" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1677,11 +991,8 @@
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="25" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1699,11 +1010,8 @@
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="26" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1721,11 +1029,8 @@
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="27" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -1743,11 +1048,8 @@
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1765,11 +1067,8 @@
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="29" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1787,11 +1086,8 @@
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="30" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1809,11 +1105,8 @@
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="31" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1831,11 +1124,8 @@
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="32" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1853,13 +1143,10 @@
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportConfirmManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportConfirmManage001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E5168D-536D-4EA3-939A-406B72F59CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094B9BD7-87D4-46FA-91F7-E40BC4AF81CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>确认状态</t>
   </si>
@@ -71,6 +71,10 @@
   </si>
   <si>
     <t>附件</t>
+  </si>
+  <si>
+    <t>复核人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -80,7 +84,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +110,15 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -158,7 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -173,6 +186,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -480,82 +496,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" style="3" customWidth="1"/>
-    <col min="4" max="6" width="36.21875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="41.77734375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="43.21875" style="5" customWidth="1"/>
-    <col min="10" max="11" width="20.44140625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="16.21875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.88671875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" style="3"/>
-    <col min="16" max="16" width="11.77734375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="40.77734375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="14.21875" customWidth="1"/>
-    <col min="22" max="22" width="14.77734375" customWidth="1"/>
-    <col min="23" max="23" width="14.44140625" customWidth="1"/>
+    <col min="2" max="3" width="20.44140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" style="3" customWidth="1"/>
+    <col min="6" max="8" width="36.21875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="24.88671875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="41.77734375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="43.21875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.88671875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="16.44140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" style="3"/>
+    <col min="17" max="17" width="11.77734375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="40.77734375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="14.21875" customWidth="1"/>
+    <col min="23" max="23" width="14.77734375" customWidth="1"/>
+    <col min="24" max="24" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -573,8 +593,9 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
-    </row>
-    <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R2" s="7"/>
+    </row>
+    <row r="3" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -592,8 +613,9 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
-    </row>
-    <row r="4" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R3" s="7"/>
+    </row>
+    <row r="4" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -611,8 +633,9 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
-    </row>
-    <row r="5" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R4" s="7"/>
+    </row>
+    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -630,8 +653,9 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
-    </row>
-    <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R5" s="7"/>
+    </row>
+    <row r="6" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -649,8 +673,9 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
-    </row>
-    <row r="7" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="7"/>
+    </row>
+    <row r="7" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -668,8 +693,9 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-    </row>
-    <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -687,8 +713,9 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-    </row>
-    <row r="9" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R8" s="7"/>
+    </row>
+    <row r="9" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -706,8 +733,9 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
-    </row>
-    <row r="10" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R9" s="7"/>
+    </row>
+    <row r="10" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -725,8 +753,9 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -744,8 +773,9 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
-    </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R11" s="7"/>
+    </row>
+    <row r="12" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -763,8 +793,9 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
-    </row>
-    <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R12" s="7"/>
+    </row>
+    <row r="13" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -782,8 +813,9 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
-    </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R13" s="7"/>
+    </row>
+    <row r="14" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -801,8 +833,9 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
-    </row>
-    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R14" s="7"/>
+    </row>
+    <row r="15" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -820,8 +853,9 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
-    </row>
-    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R15" s="7"/>
+    </row>
+    <row r="16" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -839,8 +873,9 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
-    </row>
-    <row r="17" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R16" s="7"/>
+    </row>
+    <row r="17" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -858,8 +893,9 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
-    </row>
-    <row r="18" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R17" s="7"/>
+    </row>
+    <row r="18" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -877,8 +913,9 @@
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
-    </row>
-    <row r="19" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R18" s="7"/>
+    </row>
+    <row r="19" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -896,8 +933,9 @@
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
-    </row>
-    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R19" s="7"/>
+    </row>
+    <row r="20" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -915,8 +953,9 @@
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
-    </row>
-    <row r="21" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R20" s="7"/>
+    </row>
+    <row r="21" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -934,8 +973,9 @@
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
-    </row>
-    <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="7"/>
+    </row>
+    <row r="22" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -953,8 +993,9 @@
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
-    </row>
-    <row r="23" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R22" s="7"/>
+    </row>
+    <row r="23" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -972,8 +1013,9 @@
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
-    </row>
-    <row r="24" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R23" s="7"/>
+    </row>
+    <row r="24" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -991,8 +1033,9 @@
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
-    </row>
-    <row r="25" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R24" s="7"/>
+    </row>
+    <row r="25" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1010,8 +1053,9 @@
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
-    </row>
-    <row r="26" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R25" s="7"/>
+    </row>
+    <row r="26" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1029,8 +1073,9 @@
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
-    </row>
-    <row r="27" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R26" s="7"/>
+    </row>
+    <row r="27" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -1048,8 +1093,9 @@
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
-    </row>
-    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R27" s="7"/>
+    </row>
+    <row r="28" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1067,8 +1113,9 @@
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
-    </row>
-    <row r="29" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R28" s="7"/>
+    </row>
+    <row r="29" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1086,8 +1133,9 @@
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
-    </row>
-    <row r="30" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R29" s="7"/>
+    </row>
+    <row r="30" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1105,8 +1153,9 @@
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
-    </row>
-    <row r="31" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R30" s="7"/>
+    </row>
+    <row r="31" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1124,8 +1173,9 @@
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
-    </row>
-    <row r="32" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R31" s="7"/>
+    </row>
+    <row r="32" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1143,6 +1193,7 @@
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
